--- a/data/P1/P1T2_BQ3.xlsx
+++ b/data/P1/P1T2_BQ3.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D2611E-DF8A-254F-822D-8E55F36ABBFD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDF7B16-138D-2749-9CCE-9D79C5A074EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,13 +182,56 @@
   </si>
   <si>
     <t>山</t>
+  </si>
+  <si>
+    <t>Animals make their homes in many places.</t>
+  </si>
+  <si>
+    <t>The fox is next to the pond.</t>
+  </si>
+  <si>
+    <t>Some animals live in reserves, and people help them.</t>
+  </si>
+  <si>
+    <t>The bees have food all winter long.</t>
+  </si>
+  <si>
+    <t>Polar bears live in the cold place.</t>
+  </si>
+  <si>
+    <t>動物在許多地方建造牠們的家。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狐狸在池塘旁邊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有些動物住在保護區，人們會幫助牠們。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜜蜂整個冬天都有食物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>北極熊住在寒冷的地方。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -224,6 +268,12 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -247,7 +297,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,6 +309,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,4 +930,66 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1E6591-E74A-D645-BD4A-CED89C74F033}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="54.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16">
+      <c r="A1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16">
+      <c r="A2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16">
+      <c r="A3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16">
+      <c r="A4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16">
+      <c r="A5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16">
+      <c r="A6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P1/P1T2_BQ3.xlsx
+++ b/data/P1/P1T2_BQ3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDF7B16-138D-2749-9CCE-9D79C5A074EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B07FA72-77CE-DD45-B5DB-762679B9F13D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -225,13 +225,133 @@
   <si>
     <t>chinese</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/ˈiːɡl/</t>
+  </si>
+  <si>
+    <t>ea-gle</t>
+  </si>
+  <si>
+    <t>/tʃɪk/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/nest/</t>
+  </si>
+  <si>
+    <t>/əˈpɒsəm/</t>
+  </si>
+  <si>
+    <t>o-pos-sum</t>
+  </si>
+  <si>
+    <t>/ˈhʌnɪbiː/</t>
+  </si>
+  <si>
+    <t>hon-ey-bee</t>
+  </si>
+  <si>
+    <t>/kræb/</t>
+  </si>
+  <si>
+    <t>/ˈskwɪrəl/</t>
+  </si>
+  <si>
+    <t>squir-rel</t>
+  </si>
+  <si>
+    <t>/maʊs/</t>
+  </si>
+  <si>
+    <t>/frɒɡ/</t>
+  </si>
+  <si>
+    <t>/dʒəˈræf/</t>
+  </si>
+  <si>
+    <t>gi-raffe</t>
+  </si>
+  <si>
+    <t>/ˈelɪfənt/</t>
+  </si>
+  <si>
+    <t>el-e-phant</t>
+  </si>
+  <si>
+    <t>/kəʊˈɑːlə/</t>
+  </si>
+  <si>
+    <t>ko-a-la</t>
+  </si>
+  <si>
+    <t>/ˈpærət/</t>
+  </si>
+  <si>
+    <t>par-rot</t>
+  </si>
+  <si>
+    <t>/sləʊθ/</t>
+  </si>
+  <si>
+    <t>/ˈtʃiːtə/</t>
+  </si>
+  <si>
+    <t>chee-tah</t>
+  </si>
+  <si>
+    <t>/triː ˈhɒləʊ/</t>
+  </si>
+  <si>
+    <t>tree hol-low</t>
+  </si>
+  <si>
+    <t>/haɪv/</t>
+  </si>
+  <si>
+    <t>/wʊd/</t>
+  </si>
+  <si>
+    <t>/fiːld/</t>
+  </si>
+  <si>
+    <t>/pɒnd/</t>
+  </si>
+  <si>
+    <t>/ˈdʒʌŋɡl/</t>
+  </si>
+  <si>
+    <t>jun-gle</t>
+  </si>
+  <si>
+    <t>/lænd/</t>
+  </si>
+  <si>
+    <t>/ˈɡrɑːslænd/</t>
+  </si>
+  <si>
+    <t>grass-land</t>
+  </si>
+  <si>
+    <t>/ˈmaʊntən/</t>
+  </si>
+  <si>
+    <t>moun-tain</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,6 +394,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -283,12 +411,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -297,7 +440,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -315,6 +458,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,10 +776,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -643,10 +794,18 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="D1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -656,8 +815,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -667,8 +832,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -678,8 +849,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -689,8 +866,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -700,8 +883,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -711,8 +900,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -722,8 +917,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -733,8 +934,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -744,8 +951,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -755,8 +968,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -766,8 +985,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="D12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -777,8 +1002,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -788,8 +1019,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -799,8 +1036,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -810,8 +1053,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -821,8 +1070,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -832,8 +1087,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -843,8 +1104,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -854,8 +1121,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -865,8 +1138,14 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -876,8 +1155,14 @@
       <c r="C22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -887,8 +1172,14 @@
       <c r="C23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -898,8 +1189,14 @@
       <c r="C24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -909,20 +1206,26 @@
       <c r="C25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T2_BQ3.xlsx
+++ b/data/P1/P1T2_BQ3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B07FA72-77CE-DD45-B5DB-762679B9F13D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4FB677-C556-2D4C-BA73-067E0880C6F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="128">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -345,6 +345,82 @@
   </si>
   <si>
     <t>moun-tain</t>
+  </si>
+  <si>
+    <t>a big strong bird that can fly very high</t>
+  </si>
+  <si>
+    <t>a small baby chicken</t>
+  </si>
+  <si>
+    <t>a small home birds make in trees</t>
+  </si>
+  <si>
+    <t>a small soft animal that lives in trees</t>
+  </si>
+  <si>
+    <t>a small bug that makes sweet honey</t>
+  </si>
+  <si>
+    <t>a sea animal with hard shell and two big claws</t>
+  </si>
+  <si>
+    <t>a small animal with bushy tail, likes nuts</t>
+  </si>
+  <si>
+    <t>a tiny small animal with long thin tail</t>
+  </si>
+  <si>
+    <t>a small animal that lives near water and jumps</t>
+  </si>
+  <si>
+    <t>a tall animal with long neck and spots</t>
+  </si>
+  <si>
+    <t>a very big animal with long trunk and big ears</t>
+  </si>
+  <si>
+    <t>a slow cute animal that lives in eucalyptus trees</t>
+  </si>
+  <si>
+    <t>a colorful bird that can copy people’s words</t>
+  </si>
+  <si>
+    <t>a slow animal that hangs upside down on trees</t>
+  </si>
+  <si>
+    <t>the fastest cat animal on land</t>
+  </si>
+  <si>
+    <t>an empty hole inside a tree trunk</t>
+  </si>
+  <si>
+    <t>the home where many honeybees live together</t>
+  </si>
+  <si>
+    <t>hard material from tree trunks</t>
+  </si>
+  <si>
+    <t>big open ground with grass for animals</t>
+  </si>
+  <si>
+    <t>small quiet water area, smaller than a lake</t>
+  </si>
+  <si>
+    <t>thick forest with many trees and wild animals</t>
+  </si>
+  <si>
+    <t>dry ground, not water</t>
+  </si>
+  <si>
+    <t>wide open land covered with grass</t>
+  </si>
+  <si>
+    <t>very tall high hill on the land</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -440,7 +516,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -460,6 +536,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -782,6 +861,7 @@
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -800,7 +880,9 @@
       <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="7" t="s">
+        <v>127</v>
+      </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -821,6 +903,9 @@
       <c r="E2" t="s">
         <v>66</v>
       </c>
+      <c r="F2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
@@ -838,6 +923,9 @@
       <c r="E3" t="s">
         <v>68</v>
       </c>
+      <c r="F3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
@@ -855,6 +943,9 @@
       <c r="E4" t="s">
         <v>68</v>
       </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
@@ -872,6 +963,9 @@
       <c r="E5" t="s">
         <v>71</v>
       </c>
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
@@ -889,6 +983,9 @@
       <c r="E6" t="s">
         <v>73</v>
       </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
@@ -906,6 +1003,9 @@
       <c r="E7" t="s">
         <v>68</v>
       </c>
+      <c r="F7" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
@@ -923,6 +1023,9 @@
       <c r="E8" t="s">
         <v>76</v>
       </c>
+      <c r="F8" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
@@ -940,6 +1043,9 @@
       <c r="E9" t="s">
         <v>68</v>
       </c>
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
@@ -957,6 +1063,9 @@
       <c r="E10" t="s">
         <v>68</v>
       </c>
+      <c r="F10" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
@@ -974,6 +1083,9 @@
       <c r="E11" t="s">
         <v>80</v>
       </c>
+      <c r="F11" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
@@ -991,6 +1103,9 @@
       <c r="E12" t="s">
         <v>82</v>
       </c>
+      <c r="F12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
@@ -1008,6 +1123,9 @@
       <c r="E13" t="s">
         <v>84</v>
       </c>
+      <c r="F13" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
@@ -1025,6 +1143,9 @@
       <c r="E14" t="s">
         <v>86</v>
       </c>
+      <c r="F14" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
@@ -1042,6 +1163,9 @@
       <c r="E15" t="s">
         <v>68</v>
       </c>
+      <c r="F15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
@@ -1059,8 +1183,11 @@
       <c r="E16" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1076,8 +1203,11 @@
       <c r="E17" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1093,8 +1223,11 @@
       <c r="E18" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1110,8 +1243,11 @@
       <c r="E19" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1127,8 +1263,11 @@
       <c r="E20" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1144,8 +1283,11 @@
       <c r="E21" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1161,8 +1303,11 @@
       <c r="E22" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1178,8 +1323,11 @@
       <c r="E23" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1195,8 +1343,11 @@
       <c r="E24" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1212,20 +1363,23 @@
       <c r="E25" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
